--- a/r4-JoanneumResearch-PreNUDGE-AppData-smoking/observations-summary.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-smoking/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="37">
   <si>
     <t>Profile</t>
   </si>
@@ -72,6 +72,24 @@
   </si>
   <si>
     <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>at-prenudge-sleep-duration-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Sleep Duration</t>
+  </si>
+  <si>
+    <t>LOINC#93832-4</t>
+  </si>
+  <si>
+    <t>at-prenudge-sleep-quality-observation</t>
+  </si>
+  <si>
+    <t>AT PreNUDGE Observation Sleep Quality</t>
+  </si>
+  <si>
+    <t>LOINC#61987-4</t>
   </si>
   <si>
     <t>at-prenudge-stepcount-observation</t>
@@ -238,7 +256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -404,7 +422,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -418,10 +436,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -430,13 +448,13 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>16</v>
@@ -453,10 +471,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -465,16 +483,16 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -491,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -500,7 +518,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -526,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -535,7 +553,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -561,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -570,24 +588,94 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="F10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K10" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>13</v>
       </c>
     </row>
